--- a/data/ams_weekly_data/White_Mulberry/ads_report_week18.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week18.xlsx
@@ -4077,7 +4077,7 @@
         <v>1058</v>
       </c>
       <c r="E2" t="n">
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
         <v>117.795</v>
@@ -4110,7 +4110,7 @@
         <v>1058</v>
       </c>
       <c r="E3" t="n">
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
         <v>117.795</v>
@@ -4143,7 +4143,7 @@
         <v>3177</v>
       </c>
       <c r="E4" t="n">
-        <v>53.33333333333334</v>
+        <v>53</v>
       </c>
       <c r="F4" t="n">
         <v>404.24</v>
@@ -4152,7 +4152,7 @@
         <v>6306.496666666667</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>3177</v>
       </c>
       <c r="E5" t="n">
-        <v>53.33333333333334</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
         <v>404.24</v>
@@ -4185,7 +4185,7 @@
         <v>6306.496666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>3177</v>
       </c>
       <c r="E6" t="n">
-        <v>53.33333333333334</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
         <v>404.24</v>
@@ -4218,7 +4218,7 @@
         <v>6306.496666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week18.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week18.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
